--- a/artfynd/A 52194-2025 artfynd.xlsx
+++ b/artfynd/A 52194-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129773686</v>
       </c>
       <c r="B2" t="n">
-        <v>97640</v>
+        <v>97645</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 52194-2025 artfynd.xlsx
+++ b/artfynd/A 52194-2025 artfynd.xlsx
@@ -787,7 +787,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Viveka Berg, Ingrid Runeson</t>
+          <t>Ingrid Runeson, Viveka Berg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 52194-2025 artfynd.xlsx
+++ b/artfynd/A 52194-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129773686</v>
       </c>
       <c r="B2" t="n">
-        <v>97645</v>
+        <v>97649</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ingrid Runeson, Viveka Berg</t>
+          <t>Viveka Berg, Ingrid Runeson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 52194-2025 artfynd.xlsx
+++ b/artfynd/A 52194-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129773686</v>
       </c>
       <c r="B2" t="n">
-        <v>97649</v>
+        <v>97651</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Viveka Berg, Ingrid Runeson</t>
+          <t>Ingrid Runeson, Viveka Berg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 52194-2025 artfynd.xlsx
+++ b/artfynd/A 52194-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129773686</v>
       </c>
       <c r="B2" t="n">
-        <v>97651</v>
+        <v>97661</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ingrid Runeson, Viveka Berg</t>
+          <t>Viveka Berg, Ingrid Runeson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 52194-2025 artfynd.xlsx
+++ b/artfynd/A 52194-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129773686</v>
       </c>
       <c r="B2" t="n">
-        <v>97661</v>
+        <v>97665</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Viveka Berg, Ingrid Runeson</t>
+          <t>Ingrid Runeson, Viveka Berg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 52194-2025 artfynd.xlsx
+++ b/artfynd/A 52194-2025 artfynd.xlsx
@@ -787,7 +787,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ingrid Runeson, Viveka Berg</t>
+          <t>Viveka Berg, Ingrid Runeson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 52194-2025 artfynd.xlsx
+++ b/artfynd/A 52194-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129773686</v>
       </c>
       <c r="B2" t="n">
-        <v>97665</v>
+        <v>97668</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 52194-2025 artfynd.xlsx
+++ b/artfynd/A 52194-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129773686</v>
       </c>
       <c r="B2" t="n">
-        <v>97668</v>
+        <v>97669</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 52194-2025 artfynd.xlsx
+++ b/artfynd/A 52194-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129773686</v>
       </c>
       <c r="B2" t="n">
-        <v>97669</v>
+        <v>97686</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
